--- a/en/downloads/data-excel/9.3.2.xlsx
+++ b/en/downloads/data-excel/9.3.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -283,6 +283,9 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -590,13 +593,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>12</v>
       </c>
@@ -617,7 +620,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -638,7 +641,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
@@ -653,7 +656,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:19" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -711,8 +714,11 @@
       <c r="S4" s="13">
         <v>2023</v>
       </c>
+      <c r="T4" s="13">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
@@ -770,8 +776,11 @@
       <c r="S5" s="20">
         <v>7.1262361838278068</v>
       </c>
+      <c r="T5" s="23">
+        <v>6.9662993957801538</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>13</v>
       </c>
@@ -828,6 +837,9 @@
       </c>
       <c r="S6" s="21">
         <v>10.974456007568591</v>
+      </c>
+      <c r="T6" s="21">
+        <v>9.5622119815668203</v>
       </c>
     </row>
   </sheetData>
